--- a/results/Int Task Remove ACC 0.1/Rando_10_permute.xlsx
+++ b/results/Int Task Remove ACC 0.1/Rando_10_permute.xlsx
@@ -440,97 +440,97 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6927308649954829</v>
+        <v>0.7103767140895036</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6927308649954829</v>
+        <v>0.7102334907565864</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6960819237464286</v>
+        <v>0.7186983569713039</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6829665836705814</v>
+        <v>0.7118322059086357</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6829665836705814</v>
+        <v>0.7198361867828122</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6827297143122955</v>
+        <v>0.7163210944710897</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6865312532898522</v>
+        <v>0.7211692654968871</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6715105532337871</v>
+        <v>0.7213541092855236</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6262287215420135</v>
+        <v>0.7226767828856686</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6262287215420135</v>
+        <v>0.7210884728475492</v>
       </c>
     </row>
     <row r="12">
@@ -540,787 +540,787 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.627038484231968</v>
+        <v>0.7206067772791485</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6277962213522731</v>
+        <v>0.728209855234262</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6202451689668089</v>
+        <v>0.727902598340568</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5864481347915182</v>
+        <v>0.7298397857281009</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.581980056456924</v>
+        <v>0.7297173726230435</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5788034363806851</v>
+        <v>0.7193489826246839</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5618761522133513</v>
+        <v>0.716633247888986</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5449800833878071</v>
+        <v>0.7254078192594986</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.55363775024299</v>
+        <v>0.7264728132734979</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5539554122506138</v>
+        <v>0.7203643993311348</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5428060266419882</v>
+        <v>0.7187552790651556</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5473236822841306</v>
+        <v>0.7133574731976506</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5458890006928582</v>
+        <v>0.7066265886160709</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.523014887881837</v>
+        <v>0.7066265886160709</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5413376814468249</v>
+        <v>0.7064729601692239</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5413376814468249</v>
+        <v>0.7134511192230195</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.522374667342387</v>
+        <v>0.7229081436542271</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.547798033066228</v>
+        <v>0.7206141220654518</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5453057022472598</v>
+        <v>0.6874597566917124</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5862865494928425</v>
+        <v>0.6961174235468952</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5785794203984302</v>
+        <v>0.6822210878607819</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5554868001948816</v>
+        <v>0.6822210878607819</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5359037637133282</v>
+        <v>0.6791460706617407</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5253823573336467</v>
+        <v>0.6600734968282764</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5125118434679143</v>
+        <v>0.6792948025843855</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.4918613647102604</v>
+        <v>0.6577721304531978</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4866275924035324</v>
+        <v>0.636379216213371</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.4794621412989989</v>
+        <v>0.6197463355637001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.4656857704558419</v>
+        <v>0.6197463355637001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4627539765897178</v>
+        <v>0.6138123602960439</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4799230266395399</v>
+        <v>0.5974946933918958</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4530619189968002</v>
+        <v>0.5799767659926601</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.4555199741463523</v>
+        <v>0.5736731031477306</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.4586421203908405</v>
+        <v>0.5809793293230801</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.4352630535214578</v>
+        <v>0.5809793293230801</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.4308078285628947</v>
+        <v>0.5621852453036212</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.4319352532604731</v>
+        <v>0.5852264520030457</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.3746465321591468</v>
+        <v>0.5586156791601482</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.449835721613013</v>
+        <v>0.5336317764834633</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5172345410610278</v>
+        <v>0.5324339642504768</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5322870685244079</v>
+        <v>0.5350480961089771</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5262729126729391</v>
+        <v>0.5350480961089771</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5262729126729391</v>
+        <v>0.5343423845583213</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5244685435043934</v>
+        <v>0.5473977422126903</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5313891683988121</v>
+        <v>0.549970253615471</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.519560390057118</v>
+        <v>0.549970253615471</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5262312922172196</v>
+        <v>0.549970253615471</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5306993705518138</v>
+        <v>0.5329052547049478</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5310170325594377</v>
+        <v>0.5536102072943521</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5436506770668841</v>
+        <v>0.6532520265489542</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5292463269947828</v>
+        <v>0.6582330157937388</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4986956883656137</v>
+        <v>0.6822945357238165</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4986956883656137</v>
+        <v>0.6818128401554158</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4986956883656137</v>
+        <v>0.678779443412094</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5055593911661806</v>
+        <v>0.6697833043214274</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5073221398790069</v>
+        <v>0.6697833043214274</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5149772434037698</v>
+        <v>0.6069211145468389</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5282823237924559</v>
+        <v>0.6141257378449907</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5566319747926934</v>
+        <v>0.621965073092865</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5548196487723189</v>
+        <v>0.6195902588547519</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5662218174428881</v>
+        <v>0.5917118983089854</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6095664617471288</v>
+        <v>0.5917118983089854</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.6092904201952244</v>
+        <v>0.609344894026975</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.607394853263411</v>
+        <v>0.6308993935654776</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.607394853263411</v>
+        <v>0.608387011479901</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5974824520813901</v>
+        <v>0.6355731259165682</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5968367229522125</v>
+        <v>0.5811770264877476</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.597486736540067</v>
+        <v>0.5761648219011735</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5825694755577753</v>
+        <v>0.6173537714253536</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5909590577128825</v>
+        <v>0.6352781103333798</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5600711709792803</v>
+        <v>0.6322942908976064</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5343993066521729</v>
+        <v>0.6193644066759211</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5361155383850773</v>
+        <v>0.6113989859298377</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5019635062051203</v>
+        <v>0.588672992975936</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4975786687819651</v>
+        <v>0.5988069618781109</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4956831018501517</v>
+        <v>0.6029445248290501</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4995470715112877</v>
+        <v>0.5955134372865422</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5087072441627311</v>
+        <v>0.5014285609360196</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5033382053749146</v>
+        <v>0.4929924618009905</v>
       </c>
     </row>
   </sheetData>
